--- a/订单和购物车模块测试用例.xlsx
+++ b/订单和购物车模块测试用例.xlsx
@@ -5,15 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IEDAproject\takeout\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zgl\IdeaProjects\takeout\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6FB7CB4-8B63-4C89-B049-E1FCEDB2FEC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="购物车模块测试用例" sheetId="2" r:id="rId1"/>
     <sheet name="订单模块测试用例" sheetId="3" r:id="rId2"/>
+    <sheet name="商家管理模块测试用例" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="511">
   <si>
     <t>用例编号</t>
   </si>
@@ -1002,9 +1004,6 @@
     <t>TC-CART-039</t>
   </si>
   <si>
-    <t>updateQuantity-购物车ID为空</t>
-  </si>
-  <si>
     <t>1. 调用updateQuantity方法，cartId为空 2. 验证抛出异常</t>
   </si>
   <si>
@@ -1055,26 +1054,618 @@
   </si>
   <si>
     <t>addToCart-用户ID为空</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-001</t>
+  </si>
+  <si>
+    <t>商家管理模块</t>
+  </si>
+  <si>
+    <t>创建商家-正常情况</t>
+  </si>
+  <si>
+    <t>1. 数据库中无ID为1的商家数据 2. 数据库中有对应的用户数据</t>
+  </si>
+  <si>
+    <t>1. 响应状态码200 2. 返回创建的商家DTO 3. 商家信息正确保存</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-002</t>
+  </si>
+  <si>
+    <t>创建商家-缺少必填字段name</t>
+  </si>
+  <si>
+    <t>1. 数据库连接正常</t>
+  </si>
+  <si>
+    <t>1. 发送POST请求到/merchants 2. 缺少name字段 3. 检查响应状态码 4. 检查错误信息</t>
+  </si>
+  <si>
+    <t>1. 响应状态码400 2. 返回错误信息"商家名称不能为空"</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-003</t>
+  </si>
+  <si>
+    <t>创建商家-缺少必填字段phone</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-004</t>
+  </si>
+  <si>
+    <t>获取所有商家-正常情况</t>
+  </si>
+  <si>
+    <t>1. 数据库中有多个商家数据 2. 商家数据状态正常</t>
+  </si>
+  <si>
+    <t>1. 响应状态码200 2. 返回商家DTO列表JSON格式 3. 包含所有正常状态的商家</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-005</t>
+  </si>
+  <si>
+    <t>获取所有商家-无商家数据</t>
+  </si>
+  <si>
+    <t>1. 数据库中无商家数据</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-006</t>
+  </si>
+  <si>
+    <t>获取指定商家-正常情况</t>
+  </si>
+  <si>
+    <t>1. 商家ID为1存在 2. 商家数据状态正常</t>
+  </si>
+  <si>
+    <t>id=1</t>
+  </si>
+  <si>
+    <t>1. 响应状态码200 2. 返回商家DTO 3. 商家信息正确</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-007</t>
+  </si>
+  <si>
+    <t>获取指定商家-商家不存在</t>
+  </si>
+  <si>
+    <t>1. 商家ID为999不存在</t>
+  </si>
+  <si>
+    <t>id=999</t>
+  </si>
+  <si>
+    <t>1. 响应状态码404 2. 返回错误信息"商家不存在"</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-008</t>
+  </si>
+  <si>
+    <t>获取商家菜品-正常情况</t>
+  </si>
+  <si>
+    <t>1. 商家ID为1存在 2. 商家有多个菜品数据</t>
+  </si>
+  <si>
+    <t>1. 响应状态码200 2. 返回菜品列表JSON格式 3. 包含商家的所有可用菜品</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-009</t>
+  </si>
+  <si>
+    <t>获取商家菜品-商家无菜品</t>
+  </si>
+  <si>
+    <t>1. 商家ID为2存在 2. 商家无菜品数据</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-010</t>
+  </si>
+  <si>
+    <t>获取商家今日订单数-正常情况</t>
+  </si>
+  <si>
+    <t>1. 商家ID为1存在 2. 商家有今日订单数据</t>
+  </si>
+  <si>
+    <t>1. 响应状态码200 2. 返回今日订单数量 3. 数量统计正确</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-011</t>
+  </si>
+  <si>
+    <t>获取商家今日订单数-商家无订单</t>
+  </si>
+  <si>
+    <t>1. 商家ID为3存在 2. 商家无今日订单</t>
+  </si>
+  <si>
+    <t>1. 响应状态码200 2. 返回订单数量0</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-012</t>
+  </si>
+  <si>
+    <t>更新商家-正常情况</t>
+  </si>
+  <si>
+    <t>1. 商家ID为1存在 2. 数据库中有对应的商家数据</t>
+  </si>
+  <si>
+    <t>1. 响应状态码200 2. 返回更新后的商家DTO 3. 商家信息正确更新</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-013</t>
+  </si>
+  <si>
+    <t>更新商家-商家不存在</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-014</t>
+  </si>
+  <si>
+    <t>创建商家-电话号码格式错误</t>
+  </si>
+  <si>
+    <t>1. 响应状态码400 2. 返回错误信息"联系电话格式不正确"</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-015</t>
+  </si>
+  <si>
+    <t>创建商家-电话号码长度不足</t>
+  </si>
+  <si>
+    <t>1. 响应状态码400 2. 返回错误信息"联系电话必须为11位"</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-016</t>
+  </si>
+  <si>
+    <t>创建商家-电话号码包含字母</t>
+  </si>
+  <si>
+    <t>1. 响应状态码400 2. 返回错误信息"联系电话只能包含数字"</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-017</t>
+  </si>
+  <si>
+    <t>创建商家-名称为空字符串</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-018</t>
+  </si>
+  <si>
+    <t>创建商家-名称过长</t>
+  </si>
+  <si>
+    <t>1. 响应状态码400 2. 返回错误信息"商家名称不能超过50字符"</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-019</t>
+  </si>
+  <si>
+    <t>创建商家-地址过长</t>
+  </si>
+  <si>
+    <t>1. 响应状态码400 2. 返回错误信息"地址不能超过200字符"</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-020</t>
+  </si>
+  <si>
+    <t>创建商家-描述过长</t>
+  </si>
+  <si>
+    <t>1. 响应状态码400 2. 返回错误信息"描述不能超过500字符"</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-021</t>
+  </si>
+  <si>
+    <t>获取商家-ID参数类型错误</t>
+  </si>
+  <si>
+    <t>1. 响应状态码400 2. 返回错误信息"商家ID格式不正确"</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-022</t>
+  </si>
+  <si>
+    <t>获取商家-ID为负数</t>
+  </si>
+  <si>
+    <t>1. 响应状态码400 2. 返回错误信息"商家ID必须为正数"</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-023</t>
+  </si>
+  <si>
+    <t>创建商家-缺少请求体</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-024</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-025</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-026</t>
+  </si>
+  <si>
+    <t>接口响应时间统计-创建商家</t>
+  </si>
+  <si>
+    <t>性能测试</t>
+  </si>
+  <si>
+    <t>1. 数据库连接正常 2. 网络环境稳定</t>
+  </si>
+  <si>
+    <t>1. 连续发送10次创建商家请求 2. 记录每次响应时间 3. 计算平均响应时间和P95</t>
+  </si>
+  <si>
+    <t>1. 平均响应时间&lt;500ms 2. P95响应时间&lt;1000ms 3. 无请求失败</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-027</t>
+  </si>
+  <si>
+    <t>接口响应时间统计-获取所有商家</t>
+  </si>
+  <si>
+    <t>1. 数据库中有50个商家数据 2. 网络环境稳定</t>
+  </si>
+  <si>
+    <t>1. 发送获取所有商家请求 2. 记录响应时间 3. 重复10次计算平均值</t>
+  </si>
+  <si>
+    <t>1. 平均响应时间&lt;300ms 2. P95响应时间&lt;500ms 3. 返回数据完整正确</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-028</t>
+  </si>
+  <si>
+    <t>接口响应时间统计-获取单个商家</t>
+  </si>
+  <si>
+    <t>1. 数据库中有商家数据 2. 网络环境稳定</t>
+  </si>
+  <si>
+    <t>1. 发送获取指定商家请求 2. 记录响应时间 3. 重复20次计算平均值</t>
+  </si>
+  <si>
+    <t>1. 平均响应时间&lt;200ms 2. P95响应时间&lt;300ms 3. 数据返回正确</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-029</t>
+  </si>
+  <si>
+    <t>接口响应时间统计-获取商家菜品</t>
+  </si>
+  <si>
+    <t>1. 商家有20个菜品数据 2. 网络环境稳定</t>
+  </si>
+  <si>
+    <t>1. 发送获取商家菜品请求 2. 记录响应时间 3. 重复15次计算平均值</t>
+  </si>
+  <si>
+    <t>1. 平均响应时间&lt;400ms 2. P95响应时间&lt;600ms 3. 菜品数据完整</t>
+  </si>
+  <si>
+    <t>TC-MERCHANT-030</t>
+  </si>
+  <si>
+    <t>简单并发测试-创建商家</t>
+  </si>
+  <si>
+    <t>1. 数据库连接正常 2. 无重复商家数据</t>
+  </si>
+  <si>
+    <t>1. 使用10个线程同时发送创建商家请求 2. 每个线程发送1次请求 3. 统计成功率和总耗时</t>
+  </si>
+  <si>
+    <t>1. 成功率100% 2. 总耗时&lt;5000ms 3. 所有数据正确保存</t>
+  </si>
+  <si>
+    <t>预期结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 发送POST请求到/merchants 2. 携带完整的商家信息 3. 检查响应状态码 4. 检查返回数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"name": "测试商家", "address": "测试地址", "phone": "12345678901", "description": "测试描述", "user": {"id": 1}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"address": "测试地址", "phone": "12345678901", "description": "测试描述", "user": {"id": 1}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"name": "测试商家", "address": "测试地址", "description": "测试描述", "user": {"id": 1}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>id=1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>id=999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>merchantId=1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>merchantId=2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>merchantId=3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>id=1, {"name": "更新商家", "address": "新地址", "phone": "10987654321", "description": "新描述", "user": {"id": 1}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>id=999, {"name": "更新商家", "address": "新地址", "phone": "10987654321", "description": "新描述", "user": {"id": 1}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"name": "测试商家", "address": "测试地址", "phone": "123", "description": "测试描述", "user": {"id": 1}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"name": "测试商家", "address": "测试地址", "phone": "123456", "description": "测试描述", "user": {"id": 1}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"name": "测试商家", "address": "测试地址", "phone": "1234567890a", "description": "测试描述", "user": {"id": 1}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"name": "", "address": "测试地址", "phone": "12345678901", "description": "测试描述", "user": {"id": 1}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"name": "测试商家测试商家测试商家测试商家测试商家测试商家测试商家测试商家测试商家测试商家测试商家", "address": "测试地址", "phone": "12345678901", "description": "测试描述", "user": {"id": 1}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"name": "测试商家", "address": "测试地址测试地址测试地址测试地址测试地址测试地址测试地址测试地址测试地址测试地址测试地址测试地址测试地址测试地址测试地址测试地址测试地址测试地址测试地址测试地址测试地址测试地址测试地址测试地址", "phone": "12345678901", "description": "测试描述", "user": {"id": 1}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"name": "测试商家", "address": "测试地址", "phone": "12345678901", "description": "测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述测试描述", "user": {"id": 1}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>id=abc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>id=-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"name": "并发测试商家", "address": "测试地址", "phone": "1{随机数}45678901", "description": "并发测试", "user": {"id": 1}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 响应状态码500 2. 返回错误信息"Internal Server Error"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> "status": 500,
+  "error": "Internal Server Error",</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 发送POST请求到/merchants 2. 缺少phone字段 3. 检查响应状态码 4. 检查错误信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"status": 500,
+    "error": "Internal Server Error"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"name": "测试商家","address": "测试地址","phone": "12345678901","description": "测试描述","user": {"id": 1}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 发送GET请求到/merchants 2. 检查响应状态码 3. 检查返回数据格式和数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TC-MERCHANT-031</t>
+  </si>
+  <si>
+    <t>删除商家-正常情况</t>
+  </si>
+  <si>
+    <t>1. 商家ID为4存在 2. 数据库中有对应的商家数据</t>
+  </si>
+  <si>
+    <t>id=4</t>
+  </si>
+  <si>
+    <t>1. 响应状态码200 2. 返回成功信息 3. 数据库中商家记录被删除</t>
+  </si>
+  <si>
+    <t>删除商家-商家不存在</t>
+  </si>
+  <si>
+    <t>删除商家-商家有菜品</t>
+  </si>
+  <si>
+    <t>1. 商家ID为1存在 2. 商家有菜品数据</t>
+  </si>
+  <si>
+    <t>1. 响应状态码200 2. 返回空数组[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 发送GET请求到/merchants 2. 检查响应状态码 3. 检查返回数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 发送GET请求到/merchants/{id} 2. 检查响应状态码 3. 检查返回数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当删除商家表在重复添加时商家id不会从1开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 发送GET请求到/merchants/{id} 2. 检查响应状态码 3. 检查错误信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 发送GET请求到/merchants/{merchantId}/dishes 2. 检查响应状态码 3. 检查返回数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 发送GET请求到/merchants/{merchantId}/orders/today-count 2. 检查响应状态码 3. 检查返回数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 发送PUT请求到/merchants/{id} 2. 携带更新后的商家信息 3. 检查响应状态码 4. 检查返回数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 发送PUT请求到/merchants/{id} 2. 携带更新信息 3. 检查响应状态码 4. 检查错误信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 发送POST请求到/merchants 2. 电话号码格式不正确 3. 检查响应状态码 4. 检查错误信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"message": "无权限修改此商家的信息"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>权限设置问题，商家修改权限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 发送POST请求到/merchants 2. 电话号码长度不足11位 3. 检查响应状态码 4. 检查错误信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电话号码格式和长度不足报错一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 发送POST请求到/merchants 2. 电话号码包含字母 3. 检查响应状态码 4. 检查错误信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 发送POST请求到/merchants 2. 名称为空字符串 3. 检查响应状态码 4. 检查错误信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电话号码不是数字但是不足11位时只会报错必须11位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 发送POST请求到/merchants 2. 名称超过50字符 3. 检查响应状态码 4. 检查错误信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 发送POST请求到/merchants 2. 地址超过200字符 3. 检查响应状态码 4. 检查错误信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 发送POST请求到/merchants 2. 描述超过500字符 3. 检查响应状态码 4. 检查错误信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 发送GET请求到/merchants/{id} 2. ID为字符串类型 3. 检查响应状态码 4. 检查错误信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 响应状态码400 2. 返回错误信息"描述不能超过500字符"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有设置相对应的错误信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 响应状态码400"error": "Bad Request",</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 发送GET请求到/merchants/{id} 2. ID为负数 3. 检查响应状态码 4. 检查错误信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 响应状态码404 2. "message": "商家未找到"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 发送POST请求到/merchants 2. 不携带请求体 3. 检查响应状态码 4. 检查错误信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 响应状态码400 2. 返回错误信息"error": "Bad Request",</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 发送DELETE请求到/merchants/{id} 2. 检查响应状态码 3. 检查数据库中商家是否被删除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 响应状态码500 "error": "Internal Server Error",</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格关联导致无法删除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 发送DELETE请求到/merchants/{id} 2. 检查响应状态码 3. 检查错误信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 发送DELETE请求到/merchants/{id} 2. 检查响应状态码 3. 检查级联删除是否生效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 响应状态码200 2. 商家及关联菜品被删除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
+      <family val="2"/>
       <charset val="134"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="等线"/>
+      <family val="2"/>
       <charset val="134"/>
-      <family val="2"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1100,16 +1691,19 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1122,7 +1716,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1417,22 +2011,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CE21F73-9665-41B3-AAED-3A62FCE9222C}">
   <dimension ref="A1:J42"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="13.08203125"/>
-    <col customWidth="true" max="2" min="2" width="11.5"/>
-    <col customWidth="true" max="3" min="3" width="35.08203125"/>
-    <col customWidth="true" max="4" min="4" width="11.83203125"/>
-    <col customWidth="true" max="5" min="5" width="78.08203125"/>
-    <col customWidth="true" max="6" min="6" width="89.4140625"/>
-    <col customWidth="true" max="7" min="7" width="28"/>
-    <col customWidth="true" max="8" min="8" width="75.25"/>
-    <col customWidth="true" max="9" min="9" width="11.4140625"/>
+    <col min="1" max="1" width="13.125" customWidth="1"/>
+    <col min="2" max="2" width="11.5" customWidth="1"/>
+    <col min="3" max="3" width="35.125" customWidth="1"/>
+    <col min="4" max="4" width="11.875" customWidth="1"/>
+    <col min="5" max="5" width="78.125" customWidth="1"/>
+    <col min="6" max="6" width="89.375" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="8" max="8" width="75.25" customWidth="1"/>
+    <col min="9" max="9" width="11.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1461,10 +2055,10 @@
         <v>233</v>
       </c>
       <c r="J1" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1475,7 +2069,7 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E2" t="s">
         <v>184</v>
@@ -1493,7 +2087,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1504,7 +2098,7 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E3" t="s">
         <v>187</v>
@@ -1522,7 +2116,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1533,7 +2127,7 @@
         <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E4" t="s">
         <v>190</v>
@@ -1551,7 +2145,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1562,7 +2156,7 @@
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E5" t="s">
         <v>191</v>
@@ -1580,7 +2174,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -1591,7 +2185,7 @@
         <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E6" t="s">
         <v>194</v>
@@ -1609,7 +2203,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1620,7 +2214,7 @@
         <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E7" t="s">
         <v>196</v>
@@ -1638,7 +2232,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1649,7 +2243,7 @@
         <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E8" t="s">
         <v>199</v>
@@ -1667,7 +2261,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -1678,7 +2272,7 @@
         <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E9" t="s">
         <v>202</v>
@@ -1696,7 +2290,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -1707,7 +2301,7 @@
         <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E10" t="s">
         <v>202</v>
@@ -1725,7 +2319,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -1736,7 +2330,7 @@
         <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E11" t="s">
         <v>190</v>
@@ -1754,7 +2348,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -1765,7 +2359,7 @@
         <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E12" t="s">
         <v>208</v>
@@ -1783,7 +2377,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -1794,7 +2388,7 @@
         <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E13" t="s">
         <v>211</v>
@@ -1812,7 +2406,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>45</v>
       </c>
@@ -1823,7 +2417,7 @@
         <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E14" t="s">
         <v>211</v>
@@ -1841,7 +2435,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>48</v>
       </c>
@@ -1852,7 +2446,7 @@
         <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E15" t="s">
         <v>214</v>
@@ -1870,7 +2464,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>51</v>
       </c>
@@ -1881,7 +2475,7 @@
         <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E16" t="s">
         <v>211</v>
@@ -1899,7 +2493,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>54</v>
       </c>
@@ -1910,7 +2504,7 @@
         <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E17" t="s">
         <v>214</v>
@@ -1928,7 +2522,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>57</v>
       </c>
@@ -1939,7 +2533,7 @@
         <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E18" t="s">
         <v>221</v>
@@ -1957,7 +2551,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>59</v>
       </c>
@@ -1968,7 +2562,7 @@
         <v>60</v>
       </c>
       <c r="D19" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E19" t="s">
         <v>224</v>
@@ -1986,7 +2580,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>61</v>
       </c>
@@ -1997,7 +2591,7 @@
         <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E20" t="s">
         <v>227</v>
@@ -2015,7 +2609,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>63</v>
       </c>
@@ -2026,7 +2620,7 @@
         <v>64</v>
       </c>
       <c r="D21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E21" t="s">
         <v>230</v>
@@ -2044,7 +2638,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>236</v>
       </c>
@@ -2055,7 +2649,7 @@
         <v>237</v>
       </c>
       <c r="D22" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E22" t="s">
         <v>238</v>
@@ -2073,7 +2667,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>241</v>
       </c>
@@ -2084,7 +2678,7 @@
         <v>242</v>
       </c>
       <c r="D23" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E23" t="s">
         <v>243</v>
@@ -2102,7 +2696,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>246</v>
       </c>
@@ -2113,7 +2707,7 @@
         <v>247</v>
       </c>
       <c r="D24" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E24" t="s">
         <v>243</v>
@@ -2131,7 +2725,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>248</v>
       </c>
@@ -2142,7 +2736,7 @@
         <v>249</v>
       </c>
       <c r="D25" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E25" t="s">
         <v>250</v>
@@ -2160,7 +2754,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>253</v>
       </c>
@@ -2171,7 +2765,7 @@
         <v>254</v>
       </c>
       <c r="D26" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E26" t="s">
         <v>255</v>
@@ -2189,7 +2783,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>259</v>
       </c>
@@ -2200,7 +2794,7 @@
         <v>260</v>
       </c>
       <c r="D27" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E27" t="s">
         <v>261</v>
@@ -2218,7 +2812,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>264</v>
       </c>
@@ -2229,7 +2823,7 @@
         <v>265</v>
       </c>
       <c r="D28" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E28" t="s">
         <v>250</v>
@@ -2247,7 +2841,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>268</v>
       </c>
@@ -2258,7 +2852,7 @@
         <v>269</v>
       </c>
       <c r="D29" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E29" t="s">
         <v>250</v>
@@ -2276,7 +2870,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>273</v>
       </c>
@@ -2287,7 +2881,7 @@
         <v>274</v>
       </c>
       <c r="D30" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E30" t="s">
         <v>250</v>
@@ -2305,7 +2899,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>278</v>
       </c>
@@ -2316,7 +2910,7 @@
         <v>279</v>
       </c>
       <c r="D31" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E31" t="s">
         <v>221</v>
@@ -2334,7 +2928,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>282</v>
       </c>
@@ -2345,7 +2939,7 @@
         <v>283</v>
       </c>
       <c r="D32" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E32" t="s">
         <v>284</v>
@@ -2363,7 +2957,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>287</v>
       </c>
@@ -2374,7 +2968,7 @@
         <v>288</v>
       </c>
       <c r="D33" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E33" t="s">
         <v>221</v>
@@ -2392,7 +2986,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>291</v>
       </c>
@@ -2403,7 +2997,7 @@
         <v>292</v>
       </c>
       <c r="D34" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E34" t="s">
         <v>221</v>
@@ -2421,7 +3015,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>296</v>
       </c>
@@ -2432,7 +3026,7 @@
         <v>297</v>
       </c>
       <c r="D35" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E35" t="s">
         <v>221</v>
@@ -2450,7 +3044,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>300</v>
       </c>
@@ -2461,7 +3055,7 @@
         <v>301</v>
       </c>
       <c r="D36" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E36" t="s">
         <v>302</v>
@@ -2479,7 +3073,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>305</v>
       </c>
@@ -2490,7 +3084,7 @@
         <v>306</v>
       </c>
       <c r="D37" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E37" t="s">
         <v>221</v>
@@ -2505,10 +3099,10 @@
         <v>308</v>
       </c>
       <c r="I37" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>309</v>
       </c>
@@ -2519,7 +3113,7 @@
         <v>310</v>
       </c>
       <c r="D38" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E38" t="s">
         <v>311</v>
@@ -2537,7 +3131,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>313</v>
       </c>
@@ -2548,7 +3142,7 @@
         <v>314</v>
       </c>
       <c r="D39" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E39" t="s">
         <v>255</v>
@@ -2566,7 +3160,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>318</v>
       </c>
@@ -2574,19 +3168,19 @@
         <v>9</v>
       </c>
       <c r="C40" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D40" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E40" t="s">
         <v>284</v>
       </c>
       <c r="F40" t="s">
+        <v>319</v>
+      </c>
+      <c r="G40" t="s">
         <v>320</v>
-      </c>
-      <c r="G40" t="s">
-        <v>321</v>
       </c>
       <c r="H40" t="s">
         <v>317</v>
@@ -2595,50 +3189,50 @@
         <v>235</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B41" t="s">
         <v>9</v>
       </c>
       <c r="C41" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D41" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E41" t="s">
         <v>302</v>
       </c>
       <c r="F41" t="s">
+        <v>323</v>
+      </c>
+      <c r="G41" t="s">
         <v>324</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
         <v>325</v>
-      </c>
-      <c r="H41" t="s">
-        <v>326</v>
       </c>
       <c r="I41" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B42" t="s">
         <v>9</v>
       </c>
       <c r="C42" t="s">
+        <v>327</v>
+      </c>
+      <c r="D42" t="s">
+        <v>331</v>
+      </c>
+      <c r="E42" t="s">
         <v>328</v>
-      </c>
-      <c r="D42" t="s">
-        <v>332</v>
-      </c>
-      <c r="E42" t="s">
-        <v>329</v>
       </c>
       <c r="F42" t="s">
         <v>251</v>
@@ -2647,7 +3241,7 @@
         <v>20</v>
       </c>
       <c r="H42" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I42" t="s">
         <v>235</v>
@@ -2656,25 +3250,25 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup r:id="rId1" orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD0FFDB7-6E6D-4914-8753-9A0C3F34EBC9}">
   <dimension ref="A1:I24"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="41.6640625" customWidth="1"/>
+    <col min="3" max="3" width="41.625" customWidth="1"/>
     <col min="4" max="4" width="14.5" customWidth="1"/>
-    <col min="5" max="5" width="41.4140625" customWidth="1"/>
-    <col min="6" max="6" width="87.9140625" customWidth="1"/>
-    <col min="7" max="7" width="49.9140625" customWidth="1"/>
+    <col min="5" max="5" width="41.375" customWidth="1"/>
+    <col min="6" max="6" width="87.875" customWidth="1"/>
+    <col min="7" max="7" width="49.875" customWidth="1"/>
     <col min="8" max="8" width="39.5" customWidth="1"/>
     <col min="9" max="9" width="12.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2703,7 +3297,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>65</v>
       </c>
@@ -2732,7 +3326,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -2761,7 +3355,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>78</v>
       </c>
@@ -2790,7 +3384,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>82</v>
       </c>
@@ -2819,7 +3413,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>86</v>
       </c>
@@ -2848,7 +3442,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>91</v>
       </c>
@@ -2877,7 +3471,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>96</v>
       </c>
@@ -2906,7 +3500,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>101</v>
       </c>
@@ -2935,7 +3529,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>106</v>
       </c>
@@ -2964,7 +3558,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>112</v>
       </c>
@@ -2993,7 +3587,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>118</v>
       </c>
@@ -3022,7 +3616,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>124</v>
       </c>
@@ -3033,7 +3627,7 @@
         <v>125</v>
       </c>
       <c r="D13" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E13" t="s">
         <v>127</v>
@@ -3051,7 +3645,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>130</v>
       </c>
@@ -3080,7 +3674,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>135</v>
       </c>
@@ -3109,7 +3703,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>140</v>
       </c>
@@ -3138,7 +3732,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>144</v>
       </c>
@@ -3167,7 +3761,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>149</v>
       </c>
@@ -3196,7 +3790,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>154</v>
       </c>
@@ -3225,7 +3819,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>159</v>
       </c>
@@ -3254,7 +3848,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>164</v>
       </c>
@@ -3283,7 +3877,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>169</v>
       </c>
@@ -3312,7 +3906,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>174</v>
       </c>
@@ -3341,7 +3935,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>179</v>
       </c>
@@ -3374,4 +3968,1031 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{979B9E80-60CB-4BC8-9896-6CEF2FE47731}">
+  <dimension ref="A1:J32"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18.625" customWidth="1"/>
+    <col min="2" max="2" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="28.5" customWidth="1"/>
+    <col min="4" max="4" width="11.5" customWidth="1"/>
+    <col min="5" max="5" width="51.125" customWidth="1"/>
+    <col min="6" max="6" width="86.125" customWidth="1"/>
+    <col min="7" max="7" width="91.375" customWidth="1"/>
+    <col min="8" max="8" width="67.125" customWidth="1"/>
+    <col min="9" max="9" width="65.375" customWidth="1"/>
+    <col min="10" max="10" width="47.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>441</v>
+      </c>
+      <c r="I1" t="s">
+        <v>233</v>
+      </c>
+      <c r="J1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F2" t="s">
+        <v>442</v>
+      </c>
+      <c r="G2" t="s">
+        <v>467</v>
+      </c>
+      <c r="H2" t="s">
+        <v>339</v>
+      </c>
+      <c r="I2" t="s">
+        <v>339</v>
+      </c>
+      <c r="J2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C3" t="s">
+        <v>341</v>
+      </c>
+      <c r="D3" t="s">
+        <v>330</v>
+      </c>
+      <c r="E3" t="s">
+        <v>342</v>
+      </c>
+      <c r="F3" t="s">
+        <v>343</v>
+      </c>
+      <c r="G3" t="s">
+        <v>444</v>
+      </c>
+      <c r="H3" t="s">
+        <v>463</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="J3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>345</v>
+      </c>
+      <c r="B4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C4" t="s">
+        <v>346</v>
+      </c>
+      <c r="D4" t="s">
+        <v>330</v>
+      </c>
+      <c r="E4" t="s">
+        <v>342</v>
+      </c>
+      <c r="F4" t="s">
+        <v>465</v>
+      </c>
+      <c r="G4" t="s">
+        <v>445</v>
+      </c>
+      <c r="H4" t="s">
+        <v>463</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="J4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>347</v>
+      </c>
+      <c r="B5" t="s">
+        <v>336</v>
+      </c>
+      <c r="C5" t="s">
+        <v>348</v>
+      </c>
+      <c r="D5" t="s">
+        <v>330</v>
+      </c>
+      <c r="E5" t="s">
+        <v>349</v>
+      </c>
+      <c r="F5" t="s">
+        <v>468</v>
+      </c>
+      <c r="H5" t="s">
+        <v>350</v>
+      </c>
+      <c r="I5" t="s">
+        <v>350</v>
+      </c>
+      <c r="J5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>351</v>
+      </c>
+      <c r="B6" t="s">
+        <v>336</v>
+      </c>
+      <c r="C6" t="s">
+        <v>352</v>
+      </c>
+      <c r="D6" t="s">
+        <v>330</v>
+      </c>
+      <c r="E6" t="s">
+        <v>353</v>
+      </c>
+      <c r="F6" t="s">
+        <v>478</v>
+      </c>
+      <c r="H6" t="s">
+        <v>477</v>
+      </c>
+      <c r="I6" t="s">
+        <v>477</v>
+      </c>
+      <c r="J6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>354</v>
+      </c>
+      <c r="B7" t="s">
+        <v>336</v>
+      </c>
+      <c r="C7" t="s">
+        <v>355</v>
+      </c>
+      <c r="D7" t="s">
+        <v>330</v>
+      </c>
+      <c r="E7" t="s">
+        <v>356</v>
+      </c>
+      <c r="F7" t="s">
+        <v>479</v>
+      </c>
+      <c r="G7" t="s">
+        <v>446</v>
+      </c>
+      <c r="H7" t="s">
+        <v>358</v>
+      </c>
+      <c r="I7" t="s">
+        <v>358</v>
+      </c>
+      <c r="J7" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>359</v>
+      </c>
+      <c r="B8" t="s">
+        <v>336</v>
+      </c>
+      <c r="C8" t="s">
+        <v>360</v>
+      </c>
+      <c r="D8" t="s">
+        <v>330</v>
+      </c>
+      <c r="E8" t="s">
+        <v>361</v>
+      </c>
+      <c r="F8" t="s">
+        <v>481</v>
+      </c>
+      <c r="G8" t="s">
+        <v>447</v>
+      </c>
+      <c r="H8" t="s">
+        <v>363</v>
+      </c>
+      <c r="I8" t="s">
+        <v>363</v>
+      </c>
+      <c r="J8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>364</v>
+      </c>
+      <c r="B9" t="s">
+        <v>336</v>
+      </c>
+      <c r="C9" t="s">
+        <v>365</v>
+      </c>
+      <c r="D9" t="s">
+        <v>330</v>
+      </c>
+      <c r="E9" t="s">
+        <v>366</v>
+      </c>
+      <c r="F9" t="s">
+        <v>482</v>
+      </c>
+      <c r="G9" t="s">
+        <v>448</v>
+      </c>
+      <c r="H9" t="s">
+        <v>367</v>
+      </c>
+      <c r="I9" t="s">
+        <v>367</v>
+      </c>
+      <c r="J9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>368</v>
+      </c>
+      <c r="B10" t="s">
+        <v>336</v>
+      </c>
+      <c r="C10" t="s">
+        <v>369</v>
+      </c>
+      <c r="D10" t="s">
+        <v>330</v>
+      </c>
+      <c r="E10" t="s">
+        <v>370</v>
+      </c>
+      <c r="F10" t="s">
+        <v>482</v>
+      </c>
+      <c r="G10" t="s">
+        <v>449</v>
+      </c>
+      <c r="H10" t="s">
+        <v>189</v>
+      </c>
+      <c r="I10" t="s">
+        <v>189</v>
+      </c>
+      <c r="J10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>371</v>
+      </c>
+      <c r="B11" t="s">
+        <v>336</v>
+      </c>
+      <c r="C11" t="s">
+        <v>372</v>
+      </c>
+      <c r="D11" t="s">
+        <v>330</v>
+      </c>
+      <c r="E11" t="s">
+        <v>373</v>
+      </c>
+      <c r="F11" t="s">
+        <v>483</v>
+      </c>
+      <c r="G11" t="s">
+        <v>448</v>
+      </c>
+      <c r="H11" t="s">
+        <v>374</v>
+      </c>
+      <c r="I11" t="s">
+        <v>374</v>
+      </c>
+      <c r="J11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>375</v>
+      </c>
+      <c r="B12" t="s">
+        <v>336</v>
+      </c>
+      <c r="C12" t="s">
+        <v>376</v>
+      </c>
+      <c r="D12" t="s">
+        <v>330</v>
+      </c>
+      <c r="E12" t="s">
+        <v>377</v>
+      </c>
+      <c r="F12" t="s">
+        <v>483</v>
+      </c>
+      <c r="G12" t="s">
+        <v>450</v>
+      </c>
+      <c r="H12" t="s">
+        <v>378</v>
+      </c>
+      <c r="I12" t="s">
+        <v>378</v>
+      </c>
+      <c r="J12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>379</v>
+      </c>
+      <c r="B13" t="s">
+        <v>336</v>
+      </c>
+      <c r="C13" t="s">
+        <v>380</v>
+      </c>
+      <c r="D13" t="s">
+        <v>330</v>
+      </c>
+      <c r="E13" t="s">
+        <v>381</v>
+      </c>
+      <c r="F13" t="s">
+        <v>484</v>
+      </c>
+      <c r="G13" t="s">
+        <v>451</v>
+      </c>
+      <c r="H13" t="s">
+        <v>382</v>
+      </c>
+      <c r="I13" t="s">
+        <v>487</v>
+      </c>
+      <c r="J13" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>383</v>
+      </c>
+      <c r="B14" t="s">
+        <v>336</v>
+      </c>
+      <c r="C14" t="s">
+        <v>384</v>
+      </c>
+      <c r="D14" t="s">
+        <v>330</v>
+      </c>
+      <c r="E14" t="s">
+        <v>361</v>
+      </c>
+      <c r="F14" t="s">
+        <v>485</v>
+      </c>
+      <c r="G14" t="s">
+        <v>452</v>
+      </c>
+      <c r="H14" t="s">
+        <v>363</v>
+      </c>
+      <c r="I14" t="s">
+        <v>363</v>
+      </c>
+      <c r="J14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>385</v>
+      </c>
+      <c r="B15" t="s">
+        <v>336</v>
+      </c>
+      <c r="C15" t="s">
+        <v>386</v>
+      </c>
+      <c r="D15" t="s">
+        <v>330</v>
+      </c>
+      <c r="E15" t="s">
+        <v>342</v>
+      </c>
+      <c r="F15" t="s">
+        <v>486</v>
+      </c>
+      <c r="G15" t="s">
+        <v>453</v>
+      </c>
+      <c r="H15" t="s">
+        <v>387</v>
+      </c>
+      <c r="I15" t="s">
+        <v>390</v>
+      </c>
+      <c r="J15" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>388</v>
+      </c>
+      <c r="B16" t="s">
+        <v>336</v>
+      </c>
+      <c r="C16" t="s">
+        <v>389</v>
+      </c>
+      <c r="D16" t="s">
+        <v>330</v>
+      </c>
+      <c r="E16" t="s">
+        <v>342</v>
+      </c>
+      <c r="F16" t="s">
+        <v>489</v>
+      </c>
+      <c r="G16" t="s">
+        <v>454</v>
+      </c>
+      <c r="H16" t="s">
+        <v>390</v>
+      </c>
+      <c r="I16" t="s">
+        <v>390</v>
+      </c>
+      <c r="J16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>391</v>
+      </c>
+      <c r="B17" t="s">
+        <v>336</v>
+      </c>
+      <c r="C17" t="s">
+        <v>392</v>
+      </c>
+      <c r="D17" t="s">
+        <v>330</v>
+      </c>
+      <c r="E17" t="s">
+        <v>342</v>
+      </c>
+      <c r="F17" t="s">
+        <v>491</v>
+      </c>
+      <c r="G17" t="s">
+        <v>455</v>
+      </c>
+      <c r="H17" t="s">
+        <v>393</v>
+      </c>
+      <c r="I17" t="s">
+        <v>393</v>
+      </c>
+      <c r="J17" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>394</v>
+      </c>
+      <c r="B18" t="s">
+        <v>336</v>
+      </c>
+      <c r="C18" t="s">
+        <v>395</v>
+      </c>
+      <c r="D18" t="s">
+        <v>330</v>
+      </c>
+      <c r="E18" t="s">
+        <v>342</v>
+      </c>
+      <c r="F18" t="s">
+        <v>492</v>
+      </c>
+      <c r="G18" t="s">
+        <v>456</v>
+      </c>
+      <c r="H18" t="s">
+        <v>344</v>
+      </c>
+      <c r="I18" t="s">
+        <v>344</v>
+      </c>
+      <c r="J18" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>396</v>
+      </c>
+      <c r="B19" t="s">
+        <v>336</v>
+      </c>
+      <c r="C19" t="s">
+        <v>397</v>
+      </c>
+      <c r="D19" t="s">
+        <v>330</v>
+      </c>
+      <c r="E19" t="s">
+        <v>342</v>
+      </c>
+      <c r="F19" t="s">
+        <v>494</v>
+      </c>
+      <c r="G19" t="s">
+        <v>457</v>
+      </c>
+      <c r="H19" t="s">
+        <v>398</v>
+      </c>
+      <c r="I19" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>399</v>
+      </c>
+      <c r="B20" t="s">
+        <v>336</v>
+      </c>
+      <c r="C20" t="s">
+        <v>400</v>
+      </c>
+      <c r="D20" t="s">
+        <v>330</v>
+      </c>
+      <c r="E20" t="s">
+        <v>342</v>
+      </c>
+      <c r="F20" t="s">
+        <v>495</v>
+      </c>
+      <c r="G20" t="s">
+        <v>458</v>
+      </c>
+      <c r="H20" t="s">
+        <v>401</v>
+      </c>
+      <c r="I20" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>402</v>
+      </c>
+      <c r="B21" t="s">
+        <v>336</v>
+      </c>
+      <c r="C21" t="s">
+        <v>403</v>
+      </c>
+      <c r="D21" t="s">
+        <v>330</v>
+      </c>
+      <c r="E21" t="s">
+        <v>342</v>
+      </c>
+      <c r="F21" t="s">
+        <v>496</v>
+      </c>
+      <c r="G21" t="s">
+        <v>459</v>
+      </c>
+      <c r="H21" t="s">
+        <v>404</v>
+      </c>
+      <c r="I21" t="s">
+        <v>498</v>
+      </c>
+      <c r="J21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>405</v>
+      </c>
+      <c r="B22" t="s">
+        <v>336</v>
+      </c>
+      <c r="C22" t="s">
+        <v>406</v>
+      </c>
+      <c r="D22" t="s">
+        <v>330</v>
+      </c>
+      <c r="E22" t="s">
+        <v>342</v>
+      </c>
+      <c r="F22" t="s">
+        <v>497</v>
+      </c>
+      <c r="G22" t="s">
+        <v>460</v>
+      </c>
+      <c r="H22" t="s">
+        <v>407</v>
+      </c>
+      <c r="I22" t="s">
+        <v>500</v>
+      </c>
+      <c r="J22" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>408</v>
+      </c>
+      <c r="B23" t="s">
+        <v>336</v>
+      </c>
+      <c r="C23" t="s">
+        <v>409</v>
+      </c>
+      <c r="D23" t="s">
+        <v>330</v>
+      </c>
+      <c r="E23" t="s">
+        <v>342</v>
+      </c>
+      <c r="F23" t="s">
+        <v>501</v>
+      </c>
+      <c r="G23" t="s">
+        <v>461</v>
+      </c>
+      <c r="H23" t="s">
+        <v>410</v>
+      </c>
+      <c r="I23" t="s">
+        <v>502</v>
+      </c>
+      <c r="J23" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>411</v>
+      </c>
+      <c r="B24" t="s">
+        <v>336</v>
+      </c>
+      <c r="C24" t="s">
+        <v>412</v>
+      </c>
+      <c r="D24" t="s">
+        <v>330</v>
+      </c>
+      <c r="E24" t="s">
+        <v>342</v>
+      </c>
+      <c r="F24" t="s">
+        <v>503</v>
+      </c>
+      <c r="H24" t="s">
+        <v>504</v>
+      </c>
+      <c r="I24" t="s">
+        <v>504</v>
+      </c>
+      <c r="J24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>413</v>
+      </c>
+      <c r="B25" t="s">
+        <v>336</v>
+      </c>
+      <c r="C25" t="s">
+        <v>470</v>
+      </c>
+      <c r="D25" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" t="s">
+        <v>471</v>
+      </c>
+      <c r="F25" t="s">
+        <v>505</v>
+      </c>
+      <c r="G25" t="s">
+        <v>472</v>
+      </c>
+      <c r="H25" t="s">
+        <v>473</v>
+      </c>
+      <c r="I25" t="s">
+        <v>506</v>
+      </c>
+      <c r="J25" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>414</v>
+      </c>
+      <c r="B26" t="s">
+        <v>336</v>
+      </c>
+      <c r="C26" t="s">
+        <v>474</v>
+      </c>
+      <c r="D26" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" t="s">
+        <v>361</v>
+      </c>
+      <c r="F26" t="s">
+        <v>508</v>
+      </c>
+      <c r="G26" t="s">
+        <v>362</v>
+      </c>
+      <c r="H26" t="s">
+        <v>363</v>
+      </c>
+      <c r="I26" t="s">
+        <v>363</v>
+      </c>
+      <c r="J26" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>415</v>
+      </c>
+      <c r="B27" t="s">
+        <v>336</v>
+      </c>
+      <c r="C27" t="s">
+        <v>475</v>
+      </c>
+      <c r="D27" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" t="s">
+        <v>476</v>
+      </c>
+      <c r="F27" t="s">
+        <v>509</v>
+      </c>
+      <c r="G27" t="s">
+        <v>357</v>
+      </c>
+      <c r="H27" t="s">
+        <v>510</v>
+      </c>
+      <c r="I27" t="s">
+        <v>506</v>
+      </c>
+      <c r="J27" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>421</v>
+      </c>
+      <c r="B28" t="s">
+        <v>336</v>
+      </c>
+      <c r="C28" t="s">
+        <v>416</v>
+      </c>
+      <c r="D28" t="s">
+        <v>417</v>
+      </c>
+      <c r="E28" t="s">
+        <v>418</v>
+      </c>
+      <c r="F28" t="s">
+        <v>419</v>
+      </c>
+      <c r="G28" t="s">
+        <v>443</v>
+      </c>
+      <c r="H28" t="s">
+        <v>420</v>
+      </c>
+      <c r="I28" t="s">
+        <v>420</v>
+      </c>
+      <c r="J28" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>426</v>
+      </c>
+      <c r="B29" t="s">
+        <v>336</v>
+      </c>
+      <c r="C29" t="s">
+        <v>422</v>
+      </c>
+      <c r="D29" t="s">
+        <v>417</v>
+      </c>
+      <c r="E29" t="s">
+        <v>423</v>
+      </c>
+      <c r="F29" t="s">
+        <v>424</v>
+      </c>
+      <c r="H29" t="s">
+        <v>425</v>
+      </c>
+      <c r="I29" t="s">
+        <v>425</v>
+      </c>
+      <c r="J29" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>431</v>
+      </c>
+      <c r="B30" t="s">
+        <v>336</v>
+      </c>
+      <c r="C30" t="s">
+        <v>427</v>
+      </c>
+      <c r="D30" t="s">
+        <v>417</v>
+      </c>
+      <c r="E30" t="s">
+        <v>428</v>
+      </c>
+      <c r="F30" t="s">
+        <v>429</v>
+      </c>
+      <c r="G30" t="s">
+        <v>446</v>
+      </c>
+      <c r="H30" t="s">
+        <v>430</v>
+      </c>
+      <c r="I30" t="s">
+        <v>430</v>
+      </c>
+      <c r="J30" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>436</v>
+      </c>
+      <c r="B31" t="s">
+        <v>336</v>
+      </c>
+      <c r="C31" t="s">
+        <v>432</v>
+      </c>
+      <c r="D31" t="s">
+        <v>417</v>
+      </c>
+      <c r="E31" t="s">
+        <v>433</v>
+      </c>
+      <c r="F31" t="s">
+        <v>434</v>
+      </c>
+      <c r="G31" t="s">
+        <v>448</v>
+      </c>
+      <c r="H31" t="s">
+        <v>435</v>
+      </c>
+      <c r="I31" t="s">
+        <v>435</v>
+      </c>
+      <c r="J31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>469</v>
+      </c>
+      <c r="B32" t="s">
+        <v>336</v>
+      </c>
+      <c r="C32" t="s">
+        <v>437</v>
+      </c>
+      <c r="D32" t="s">
+        <v>417</v>
+      </c>
+      <c r="E32" t="s">
+        <v>438</v>
+      </c>
+      <c r="F32" t="s">
+        <v>439</v>
+      </c>
+      <c r="G32" t="s">
+        <v>462</v>
+      </c>
+      <c r="H32" t="s">
+        <v>440</v>
+      </c>
+      <c r="I32" t="s">
+        <v>440</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>